--- a/README.xlsx
+++ b/README.xlsx
@@ -1933,7 +1933,7 @@
     <col min="7" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:5">
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -1961,20 +1961,20 @@
       <c r="D2" s="8"/>
       <c r="E2" s="9"/>
     </row>
-    <row r="3" customHeight="1" spans="1:5">
+    <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="10"/>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="10"/>
     </row>
-    <row r="4" customHeight="1" spans="1:5">
+    <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" customHeight="1" spans="1:5">
+    <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="13" t="s">
         <v>8</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:4">
+    <row r="6" customHeight="1" spans="1:6">
       <c r="C6" s="17" t="s">
         <v>12</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:6">
+    <row r="7" customHeight="1" spans="1:6">
       <c r="C7" s="19" t="s">
         <v>14</v>
       </c>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="F7" s="21"/>
     </row>
-    <row r="8" customHeight="1" spans="4:6">
+    <row r="8" customHeight="1" spans="1:6">
       <c r="D8" s="20" t="s">
         <v>17</v>
       </c>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" customHeight="1" spans="4:6">
+    <row r="9" customHeight="1" spans="1:6">
       <c r="D9" s="20" t="s">
         <v>19</v>
       </c>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" customHeight="1" spans="4:6">
+    <row r="10" customHeight="1" spans="1:6">
       <c r="D10" s="22" t="s">
         <v>21</v>
       </c>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" customHeight="1" spans="4:6">
+    <row r="11" customHeight="1" spans="1:6">
       <c r="D11" s="22" t="s">
         <v>23</v>
       </c>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" customHeight="1" spans="3:5">
+    <row r="12" customHeight="1" spans="1:6">
       <c r="C12" s="23" t="s">
         <v>25</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="4:5">
+    <row r="13" customHeight="1" spans="1:6">
       <c r="D13" s="24" t="s">
         <v>28</v>
       </c>
@@ -2064,12 +2064,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="4:4">
+    <row r="14" customHeight="1" spans="1:6">
       <c r="D14" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:3">
+    <row r="16" customHeight="1" spans="1:6">
       <c r="A16" s="26" t="s">
         <v>31</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:4">
+    <row r="17" customHeight="1" spans="1:5">
       <c r="A17" s="26" t="s">
         <v>34</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:5">
+    <row r="18" customHeight="1" spans="1:5">
       <c r="C18" s="28" t="s">
         <v>38</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:3">
+    <row r="23" customHeight="1" spans="1:5">
       <c r="A23" s="26" t="s">
         <v>43</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:3">
+    <row r="24" customHeight="1" spans="1:5">
       <c r="A24" s="26" t="s">
         <v>43</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:4">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:5">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2188,12 +2188,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="5:5">
+    <row r="27" customHeight="1" spans="1:5">
       <c r="E27" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:1">
+    <row r="28" customHeight="1" spans="1:5">
       <c r="A28" s="12" t="s">
         <v>58</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:2">
+    <row r="30" customHeight="1" spans="1:5">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
     </row>
@@ -2316,7 +2316,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:3">
+    <row r="39" customHeight="1" spans="1:5">
       <c r="C39" s="28" t="s">
         <v>80</v>
       </c>
@@ -2335,12 +2335,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:3">
+    <row r="41" customHeight="1" spans="1:5">
       <c r="C41" s="40" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:4">
+    <row r="42" customHeight="1" spans="1:5">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2360,13 +2360,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:4">
+    <row r="44" customHeight="1" spans="1:5">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="1:1">
+    <row r="45" customHeight="1" spans="1:5">
       <c r="A45" s="12" t="s">
         <v>88</v>
       </c>
@@ -2385,11 +2385,11 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:2">
+    <row r="47" customHeight="1" spans="1:5">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
     </row>
-    <row r="48" customHeight="1" spans="1:3">
+    <row r="48" customHeight="1" spans="1:5">
       <c r="A48" s="33" t="s">
         <v>93</v>
       </c>
@@ -2400,13 +2400,13 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:4">
+    <row r="49" customHeight="1" spans="1:5">
       <c r="A49" s="12"/>
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="12"/>
     </row>
-    <row r="50" customHeight="1" spans="1:1">
+    <row r="50" customHeight="1" spans="1:5">
       <c r="A50" s="12" t="s">
         <v>95</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:3">
+    <row r="52" customHeight="1" spans="1:5">
       <c r="A52" s="43" t="s">
         <v>96</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:3">
+    <row r="53" customHeight="1" spans="1:5">
       <c r="A53" s="43" t="s">
         <v>96</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:4">
+    <row r="54" customHeight="1" spans="1:5">
       <c r="A54" s="47"/>
       <c r="B54" s="47"/>
       <c r="C54" s="47"/>
@@ -2467,13 +2467,13 @@
         <v>104</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:4">
+    <row r="56" customHeight="1" spans="1:5">
       <c r="A56" s="47"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
       <c r="D56" s="47"/>
     </row>
-    <row r="57" customHeight="1" spans="1:4">
+    <row r="57" customHeight="1" spans="1:5">
       <c r="A57" s="43" t="s">
         <v>96</v>
       </c>
@@ -2483,18 +2483,18 @@
       <c r="C57" s="47"/>
       <c r="D57" s="47"/>
     </row>
-    <row r="58" customHeight="1" spans="1:4">
+    <row r="58" customHeight="1" spans="1:5">
       <c r="A58" s="47"/>
       <c r="B58" s="47"/>
       <c r="C58" s="47"/>
       <c r="D58" s="47"/>
     </row>
-    <row r="59" customHeight="1" spans="1:1">
+    <row r="59" customHeight="1" spans="1:5">
       <c r="A59" s="12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:3">
+    <row r="60" customHeight="1" spans="1:5">
       <c r="A60" s="43" t="s">
         <v>107</v>
       </c>
@@ -2505,13 +2505,13 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:4">
+    <row r="61" customHeight="1" spans="1:5">
       <c r="A61" s="49"/>
       <c r="B61" s="49"/>
       <c r="C61" s="47"/>
       <c r="D61" s="47"/>
     </row>
-    <row r="62" customHeight="1" spans="1:1">
+    <row r="62" customHeight="1" spans="1:5">
       <c r="A62" s="12" t="s">
         <v>110</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:4">
+    <row r="65" customHeight="1" spans="1:4">
       <c r="C65" s="32" t="s">
         <v>117</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:4">
+    <row r="66" customHeight="1" spans="1:4">
       <c r="C66" s="28" t="s">
         <v>118</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:3">
+    <row r="67" customHeight="1" spans="1:4">
       <c r="A67" s="50" t="s">
         <v>120</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:2">
+    <row r="68" customHeight="1" spans="1:4">
       <c r="A68" s="2" t="s">
         <v>123</v>
       </c>
@@ -2582,10 +2582,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="2:2">
+    <row r="69" customHeight="1" spans="1:4">
       <c r="B69" s="1"/>
     </row>
-    <row r="70" customHeight="1" spans="1:2">
+    <row r="70" customHeight="1" spans="1:4">
       <c r="A70" s="2" t="s">
         <v>125</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:2">
+    <row r="71" customHeight="1" spans="1:4">
       <c r="A71" s="50" t="s">
         <v>127</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:2">
+    <row r="72" customHeight="1" spans="1:4">
       <c r="A72" s="2" t="s">
         <v>128</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:2">
+    <row r="73" customHeight="1" spans="1:4">
       <c r="A73" s="50" t="s">
         <v>129</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:3">
+    <row r="74" customHeight="1" spans="1:4">
       <c r="A74" s="50" t="s">
         <v>127</v>
       </c>
@@ -2628,10 +2628,10 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="2:2">
+    <row r="75" customHeight="1" spans="1:4">
       <c r="B75" s="1"/>
     </row>
-    <row r="76" customHeight="1" spans="1:2">
+    <row r="76" customHeight="1" spans="1:4">
       <c r="A76" s="2" t="s">
         <v>124</v>
       </c>
@@ -2639,10 +2639,10 @@
         <v>124</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="2:2">
+    <row r="77" customHeight="1" spans="1:4">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" customHeight="1" spans="1:2">
+    <row r="78" customHeight="1" spans="1:4">
       <c r="A78" s="50" t="s">
         <v>133</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:2">
+    <row r="79" customHeight="1" spans="1:4">
       <c r="A79" s="50" t="s">
         <v>120</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="1:1">
+    <row r="81" customHeight="1" spans="1:3">
       <c r="A81" s="12" t="s">
         <v>134</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="1:2">
+    <row r="83" customHeight="1" spans="1:3">
       <c r="A83" s="26" t="s">
         <v>138</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:1">
+    <row r="84" customHeight="1" spans="1:3">
       <c r="A84" s="1" t="s">
         <v>139</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="1:2">
+    <row r="86" customHeight="1" spans="1:3">
       <c r="A86" s="1" t="s">
         <v>135</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="1:2">
+    <row r="87" customHeight="1" spans="1:3">
       <c r="A87" s="1" t="s">
         <v>138</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:2">
+    <row r="88" customHeight="1" spans="1:3">
       <c r="A88" s="1" t="s">
         <v>138</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:1">
+    <row r="90" customHeight="1" spans="1:3">
       <c r="A90" s="12" t="s">
         <v>143</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:2">
+    <row r="92" customHeight="1" spans="1:3">
       <c r="A92" s="52" t="s">
         <v>147</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="2:2">
+    <row r="93" customHeight="1" spans="1:3">
       <c r="B93" s="1"/>
     </row>
     <row r="94" customHeight="1" spans="1:3">
@@ -2760,7 +2760,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:2">
+    <row r="95" customHeight="1" spans="1:3">
       <c r="A95" s="52" t="s">
         <v>147</v>
       </c>
@@ -2768,10 +2768,10 @@
         <v>131</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="2:2">
+    <row r="96" customHeight="1" spans="1:3">
       <c r="B96" s="1"/>
     </row>
-    <row r="97" customHeight="1" spans="1:4">
+    <row r="97" customHeight="1" spans="1:5">
       <c r="A97" s="52" t="s">
         <v>147</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="1:4">
+    <row r="98" customHeight="1" spans="1:5">
       <c r="A98" s="52" t="s">
         <v>147</v>
       </c>
@@ -2799,10 +2799,10 @@
         <v>154</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="2:2">
+    <row r="99" customHeight="1" spans="1:5">
       <c r="B99" s="1"/>
     </row>
-    <row r="100" customHeight="1" spans="1:1">
+    <row r="100" customHeight="1" spans="1:5">
       <c r="A100" s="12" t="s">
         <v>155</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:3">
+    <row r="104" customHeight="1" spans="1:5">
       <c r="A104" s="52" t="s">
         <v>159</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:2">
+    <row r="107" customHeight="1" spans="1:5">
       <c r="A107" s="52" t="s">
         <v>159</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:2">
+    <row r="108" customHeight="1" spans="1:5">
       <c r="A108" s="52" t="s">
         <v>159</v>
       </c>
@@ -2904,12 +2904,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:1">
+    <row r="109" customHeight="1" spans="1:5">
       <c r="A109" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:2">
+    <row r="110" customHeight="1" spans="1:5">
       <c r="A110" s="2" t="s">
         <v>156</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:2">
+    <row r="111" customHeight="1" spans="1:5">
       <c r="A111" s="2" t="s">
         <v>170</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:2">
+    <row r="112" customHeight="1" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>171</v>
       </c>
